--- a/satisfaction_surveys/011_wayfinder_feedback_survey--satisfaction_surveys.xlsx
+++ b/satisfaction_surveys/011_wayfinder_feedback_survey--satisfaction_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -750,8 +750,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -779,12 +779,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'seldom'}</t>
+          <t>seldom</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'Seldom'}</t>
+          <t>Seldom</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_30,_'name':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 30, 'name': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_40,_'name':_'happy'}</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 40, 'name': 'Happy'}</t>
+          <t>Happy</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_50,_'name':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 50, 'name': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_60,_'name':_'sad'}</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 60, 'name': 'Sad'}</t>
+          <t>Sad</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_70,_'name':_'very_helpful'}</t>
+          <t>very_helpful</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 70, 'name': 'Very Helpful'}</t>
+          <t>Very Helpful</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_80,_'name':_'not_helpful'}</t>
+          <t>not_helpful</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 80, 'name': 'Not Helpful'}</t>
+          <t>Not Helpful</t>
         </is>
       </c>
     </row>
